--- a/artfynd/A 17740-2025 artfynd.xlsx
+++ b/artfynd/A 17740-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95312943</v>
+        <v>95312942</v>
       </c>
       <c r="B2" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>390105.466477605</v>
+        <v>390190</v>
       </c>
       <c r="R2" t="n">
-        <v>6717315.984523882</v>
+        <v>6717487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95312946</v>
+        <v>95312944</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>390074.0657909829</v>
+        <v>390106</v>
       </c>
       <c r="R3" t="n">
-        <v>6717271.695073457</v>
+        <v>6717316</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95312942</v>
+        <v>95312946</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>390190.4821154769</v>
+        <v>390074</v>
       </c>
       <c r="R4" t="n">
-        <v>6717486.999011442</v>
+        <v>6717272</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95312944</v>
+        <v>95312943</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>390105.466477605</v>
+        <v>390106</v>
       </c>
       <c r="R5" t="n">
-        <v>6717315.984523882</v>
+        <v>6717316</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1066,7 @@
         <v>95312945</v>
       </c>
       <c r="B6" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>390111.5198615232</v>
+        <v>390112</v>
       </c>
       <c r="R6" t="n">
-        <v>6717304.488141487</v>
+        <v>6717304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 17740-2025 artfynd.xlsx
+++ b/artfynd/A 17740-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95312942</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95312944</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95312946</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95312943</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95312945</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>